--- a/request_forms/023_payroll_statement_copy_request_form--request_forms.xlsx
+++ b/request_forms/023_payroll_statement_copy_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_1,_'value':_'january'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 1, 'value': 'January'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_2,_'value':_'february'}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 2, 'value': 'February'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_3,_'value':_'march'}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 3, 'value': 'March'}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_4,_'value':_'april'}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 4, 'value': 'April'}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_5,_'value':_'may'}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 5, 'value': 'May'}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_6,_'value':_'june'}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 6, 'value': 'June'}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_7,_'value':_'july'}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 7, 'value': 'July'}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_8,_'value':_'august'}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 8, 'value': 'August'}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_9,_'value':_'september'}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 9, 'value': 'September'}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_10,_'value':_'october'}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 10, 'value': 'October'}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_11,_'value':_'november'}</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 11, 'value': 'November'}</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_12,_'value':_'december'}</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 12, 'value': 'December'}</t>
+          <t>12</t>
         </is>
       </c>
     </row>
